--- a/data/trans_dic/Hacinamiento_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/Hacinamiento_R-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con dos o más personas por habitación</t>
+          <t>Hogares con dos o más personas por habitación (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,03; 9,72</t>
+          <t>1,45; 8,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,47; 14,83</t>
+          <t>4,79; 14,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,59; 17,05</t>
+          <t>5,85; 16,96</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,91; 9,68</t>
+          <t>2,08; 9,77</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,45; 10,66</t>
+          <t>3,64; 11,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,19; 13,05</t>
+          <t>4,49; 13,15</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,53; 14,2</t>
+          <t>4,55; 14,28</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,22; 8,57</t>
+          <t>2,03; 8,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,61; 8,54</t>
+          <t>3,44; 8,11</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,48; 11,8</t>
+          <t>5,4; 11,58</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,31; 13,5</t>
+          <t>6,43; 13,35</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,66; 7,31</t>
+          <t>2,72; 7,1</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,71; 11,05</t>
+          <t>4,09; 11,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,26; 16,39</t>
+          <t>7,54; 16,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,82; 11,84</t>
+          <t>4,79; 11,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,44; 9,37</t>
+          <t>3,28; 9,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,81; 12,32</t>
+          <t>4,75; 12,01</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,53; 12,07</t>
+          <t>4,8; 12,4</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,24; 9,11</t>
+          <t>3,02; 8,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,88; 12,03</t>
+          <t>4,9; 12,23</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,42; 10,72</t>
+          <t>5,22; 10,64</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,82; 12,38</t>
+          <t>7,04; 12,55</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,62; 8,88</t>
+          <t>4,67; 9,45</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,87; 9,65</t>
+          <t>4,97; 9,78</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,9; 11,98</t>
+          <t>3,66; 11,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,71; 20,59</t>
+          <t>9,68; 20,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,61; 15,79</t>
+          <t>6,44; 15,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,76; 9,0</t>
+          <t>2,61; 8,92</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,91; 10,03</t>
+          <t>2,58; 10,12</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,62; 18,92</t>
+          <t>8,41; 19,24</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,01; 12,3</t>
+          <t>4,04; 11,46</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,7; 14,91</t>
+          <t>6,69; 15,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,27; 9,64</t>
+          <t>4,18; 9,52</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10,49; 18,39</t>
+          <t>10,55; 17,88</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,14; 12,09</t>
+          <t>6,13; 11,7</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,45; 10,59</t>
+          <t>5,35; 10,49</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,54; 12,01</t>
+          <t>4,51; 11,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,03; 11,0</t>
+          <t>3,77; 11,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,03; 10,87</t>
+          <t>3,98; 10,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,26; 11,79</t>
+          <t>4,93; 11,9</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,23; 15,19</t>
+          <t>7,17; 15,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,9; 12,48</t>
+          <t>4,86; 12,44</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,26; 9,94</t>
+          <t>3,28; 9,75</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,12; 13,72</t>
+          <t>5,95; 13,8</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,37; 11,84</t>
+          <t>6,45; 11,76</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,26; 10,45</t>
+          <t>5,36; 10,53</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,37; 9,1</t>
+          <t>4,42; 9,0</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,22; 11,36</t>
+          <t>6,46; 11,74</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,96; 8,53</t>
+          <t>5,06; 8,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,93; 12,53</t>
+          <t>8,05; 12,88</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,55; 10,48</t>
+          <t>6,66; 10,78</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,46; 7,65</t>
+          <t>4,54; 7,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,3; 9,94</t>
+          <t>6,36; 10,16</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,17; 11,56</t>
+          <t>7,33; 11,64</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,07; 8,45</t>
+          <t>5,07; 8,64</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,36; 10,31</t>
+          <t>6,52; 10,23</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,97; 8,62</t>
+          <t>6,0; 8,64</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,28; 11,27</t>
+          <t>8,21; 11,23</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6,37; 8,9</t>
+          <t>6,39; 9,04</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,98; 8,59</t>
+          <t>6,02; 8,46</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Hogares con dos o más personas por habitación (tasa de respuesta: 99,79%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>4904</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>8451</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>9516</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>5288</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>7577</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>8687</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>8994</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>6294</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>12481</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>17138</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>18510</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>11583</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>1521; 9431</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>4654; 14448</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>5274; 15279</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2392; 11247</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>4307; 13416</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>5056; 14794</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>4761; 14946</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2846; 11232</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>7689; 18128</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>11314; 24284</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>12528; 25992</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>6959; 18135</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>8364</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>14676</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>11666</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>10807</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>11379</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>12243</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>9653</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>19845</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>19743</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>26919</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>21318</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>30651</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>5079; 13985</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>9721; 20933</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>7283; 17728</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>6169; 17379</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>6687; 16909</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>7420; 19170</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>5288; 15567</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>12478; 31138</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>13832; 28214</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>19974; 35595</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>15294; 30917</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>21979; 43261</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>7588</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>15421</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>12304</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>10232</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>6631</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>15479</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>9564</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>18870</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>14219</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>30899</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>21867</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>29102</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>3927; 12473</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>10150; 21890</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>7505; 17918</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>4949; 16939</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2901; 11391</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>9818; 22467</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>5364; 15229</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>12311; 27593</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>9204; 20944</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>23375; 39630</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>15287; 29170</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>20002; 39243</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>12105</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>9942</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>11237</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>13110</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>16564</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>12978</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>9535</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>17078</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>28669</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>22920</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>20772</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>30188</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>7460; 18735</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>5505; 16240</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>6606; 17624</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>8252; 19898</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>11260; 24280</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>7537; 19282</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>5165; 15369</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>10789; 25011</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>20781; 37911</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>16121; 31684</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>14293; 29118</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>22496; 40921</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>32961</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>48489</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>44723</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>39438</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>42151</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>49386</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>37745</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>62086</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>75112</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>97876</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>82468</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>101524</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>25409; 43683</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>38389; 61454</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>34963; 56558</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>29988; 51536</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>33619; 53681</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>39493; 62706</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>28904; 49272</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>49592; 77792</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>61797; 89101</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>83350; 114106</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>70008; 99045</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>85519; 120247</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/Hacinamiento_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/Hacinamiento_R-Habitat-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,45; 8,96</t>
+          <t>2,06; 9,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,79; 14,88</t>
+          <t>4,42; 14,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,85; 16,96</t>
+          <t>5,79; 17,16</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,08; 9,77</t>
+          <t>2,06; 9,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,64; 11,34</t>
+          <t>3,25; 10,48</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,49; 13,15</t>
+          <t>4,32; 13,51</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,55; 14,28</t>
+          <t>4,67; 14,58</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,03; 8,0</t>
+          <t>2,14; 8,25</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,44; 8,11</t>
+          <t>3,39; 8,5</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,4; 11,58</t>
+          <t>5,21; 11,54</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,43; 13,35</t>
+          <t>6,57; 14,09</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,72; 7,1</t>
+          <t>2,64; 7,13</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,09; 11,25</t>
+          <t>3,64; 10,84</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,54; 16,23</t>
+          <t>7,62; 16,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,79; 11,67</t>
+          <t>4,81; 11,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,28; 9,25</t>
+          <t>3,47; 9,17</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,75; 12,01</t>
+          <t>4,77; 12,73</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,8; 12,4</t>
+          <t>5,03; 12,04</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,02; 8,88</t>
+          <t>3,24; 9,45</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,9; 12,23</t>
+          <t>4,92; 12,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,22; 10,64</t>
+          <t>5,18; 10,24</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,04; 12,55</t>
+          <t>6,93; 12,56</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,67; 9,45</t>
+          <t>4,68; 9,45</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,97; 9,78</t>
+          <t>4,85; 10,09</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,66; 11,62</t>
+          <t>3,73; 12,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,68; 20,88</t>
+          <t>9,76; 21,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,44; 15,37</t>
+          <t>6,54; 15,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,61; 8,92</t>
+          <t>2,72; 9,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,58; 10,12</t>
+          <t>2,94; 10,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,41; 19,24</t>
+          <t>8,22; 18,76</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,04; 11,46</t>
+          <t>3,78; 11,85</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,69; 15,0</t>
+          <t>6,4; 15,46</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,18; 9,52</t>
+          <t>4,12; 9,69</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10,55; 17,88</t>
+          <t>10,42; 18,13</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,13; 11,7</t>
+          <t>5,9; 11,93</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,35; 10,49</t>
+          <t>5,36; 10,71</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,51; 11,33</t>
+          <t>4,36; 11,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,77; 11,12</t>
+          <t>3,67; 11,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,98; 10,61</t>
+          <t>3,91; 10,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,93; 11,9</t>
+          <t>4,91; 11,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,17; 15,47</t>
+          <t>7,02; 14,89</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,86; 12,44</t>
+          <t>5,04; 12,68</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,28; 9,75</t>
+          <t>3,22; 10,09</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,95; 13,8</t>
+          <t>6,27; 14,6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,45; 11,76</t>
+          <t>6,55; 12,03</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,36; 10,53</t>
+          <t>5,37; 10,86</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,42; 9,0</t>
+          <t>4,24; 8,78</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,46; 11,74</t>
+          <t>6,43; 11,42</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,06; 8,7</t>
+          <t>4,96; 8,52</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,05; 12,88</t>
+          <t>8,18; 12,65</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,66; 10,78</t>
+          <t>6,62; 10,62</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,54; 7,81</t>
+          <t>4,47; 7,62</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,36; 10,16</t>
+          <t>6,19; 10,1</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,33; 11,64</t>
+          <t>7,1; 11,39</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,07; 8,64</t>
+          <t>5,02; 8,55</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,52; 10,23</t>
+          <t>6,46; 10,25</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,0; 8,64</t>
+          <t>5,97; 8,63</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,21; 11,23</t>
+          <t>8,18; 11,2</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6,39; 9,04</t>
+          <t>6,2; 8,78</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,02; 8,46</t>
+          <t>6,09; 8,67</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1521; 9431</t>
+          <t>2169; 9787</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4654; 14448</t>
+          <t>4288; 14316</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5274; 15279</t>
+          <t>5218; 15462</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2392; 11247</t>
+          <t>2373; 10701</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4307; 13416</t>
+          <t>3844; 12397</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5056; 14794</t>
+          <t>4863; 15204</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4761; 14946</t>
+          <t>4891; 15264</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2846; 11232</t>
+          <t>2998; 11579</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>7689; 18128</t>
+          <t>7587; 19008</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11314; 24284</t>
+          <t>10925; 24200</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12528; 25992</t>
+          <t>12794; 27451</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6959; 18135</t>
+          <t>6736; 18232</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5079; 13985</t>
+          <t>4522; 13470</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9721; 20933</t>
+          <t>9827; 21274</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7283; 17728</t>
+          <t>7315; 17774</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6169; 17379</t>
+          <t>6517; 17230</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6687; 16909</t>
+          <t>6718; 17919</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7420; 19170</t>
+          <t>7781; 18601</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5288; 15567</t>
+          <t>5675; 16574</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12478; 31138</t>
+          <t>12531; 30568</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13832; 28214</t>
+          <t>13722; 27132</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>19974; 35595</t>
+          <t>19646; 35616</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15294; 30917</t>
+          <t>15303; 30931</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>21979; 43261</t>
+          <t>21472; 44650</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3927; 12473</t>
+          <t>4008; 13325</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10150; 21890</t>
+          <t>10233; 22379</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7505; 17918</t>
+          <t>7619; 18284</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4949; 16939</t>
+          <t>5174; 17216</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2901; 11391</t>
+          <t>3310; 11699</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9818; 22467</t>
+          <t>9595; 21910</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5364; 15229</t>
+          <t>5024; 15741</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>12311; 27593</t>
+          <t>11773; 28436</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>9204; 20944</t>
+          <t>9057; 21306</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>23375; 39630</t>
+          <t>23097; 40184</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15287; 29170</t>
+          <t>14722; 29753</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>20002; 39243</t>
+          <t>20045; 40057</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7460; 18735</t>
+          <t>7210; 19111</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5505; 16240</t>
+          <t>5353; 16791</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6606; 17624</t>
+          <t>6502; 17873</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8252; 19898</t>
+          <t>8209; 19237</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11260; 24280</t>
+          <t>11023; 23374</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7537; 19282</t>
+          <t>7806; 19643</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5165; 15369</t>
+          <t>5078; 15892</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10789; 25011</t>
+          <t>11356; 26464</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>20781; 37911</t>
+          <t>21113; 38764</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>16121; 31684</t>
+          <t>16147; 32677</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>14293; 29118</t>
+          <t>13710; 28425</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>22496; 40921</t>
+          <t>22392; 39790</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>25409; 43683</t>
+          <t>24919; 42812</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>38389; 61454</t>
+          <t>39011; 60340</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>34963; 56558</t>
+          <t>34721; 55716</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>29988; 51536</t>
+          <t>29505; 50292</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>33619; 53681</t>
+          <t>32699; 53374</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>39493; 62706</t>
+          <t>38238; 61357</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>28904; 49272</t>
+          <t>28628; 48785</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>49592; 77792</t>
+          <t>49117; 77960</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>61797; 89101</t>
+          <t>61541; 88920</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>83350; 114106</t>
+          <t>83051; 113810</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>70008; 99045</t>
+          <t>67923; 96114</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>85519; 120247</t>
+          <t>86545; 123106</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/Hacinamiento_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/Hacinamiento_R-Habitat-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6,41%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7,72%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8,59%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4,45%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>4,66%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>8,7%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>10,56%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4,59%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>6,41%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>7,72%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>8,59%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,61%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,06; 9,3</t>
+          <t>3,45; 10,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,42; 14,74</t>
+          <t>4,19; 13,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,79; 17,16</t>
+          <t>4,53; 14,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,06; 9,29</t>
+          <t>2,23; 9,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,25; 10,48</t>
+          <t>2,03; 9,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,32; 13,51</t>
+          <t>4,47; 14,83</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,67; 14,58</t>
+          <t>5,59; 17,05</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,14; 8,25</t>
+          <t>1,99; 10,11</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,39; 8,5</t>
+          <t>3,61; 8,54</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,21; 11,54</t>
+          <t>5,48; 11,8</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,57; 14,09</t>
+          <t>6,31; 13,5</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,64; 7,13</t>
+          <t>2,68; 7,44</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>8,08%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>7,92%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>5,51%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>7,45%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>6,73%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>11,38%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>7,68%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>5,75%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>8,08%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>7,92%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>5,51%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,5%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,64; 10,84</t>
+          <t>4,81; 12,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,62; 16,49</t>
+          <t>4,53; 12,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,81; 11,7</t>
+          <t>3,24; 9,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,47; 9,17</t>
+          <t>4,69; 11,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,77; 12,73</t>
+          <t>3,71; 11,05</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,03; 12,04</t>
+          <t>7,26; 16,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,24; 9,45</t>
+          <t>4,82; 11,84</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,92; 12,0</t>
+          <t>3,16; 8,14</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,18; 10,24</t>
+          <t>5,42; 10,72</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,93; 12,56</t>
+          <t>6,82; 12,38</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,68; 9,45</t>
+          <t>4,62; 8,88</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,85; 10,09</t>
+          <t>4,65; 9,24</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>5,89%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>13,25%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>7,2%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>9,52%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>7,07%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>14,71%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>10,56%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5,39%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>5,89%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>13,25%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>7,2%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>8,03%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,73; 12,41</t>
+          <t>2,91; 10,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,76; 21,34</t>
+          <t>8,62; 18,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,54; 15,69</t>
+          <t>4,01; 12,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,72; 9,06</t>
+          <t>6,15; 14,26</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,94; 10,39</t>
+          <t>3,9; 11,98</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,22; 18,76</t>
+          <t>9,71; 20,59</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,78; 11,85</t>
+          <t>6,61; 15,79</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,4; 15,46</t>
+          <t>3,72; 10,23</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,12; 9,69</t>
+          <t>4,27; 9,64</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10,42; 18,13</t>
+          <t>10,49; 18,39</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,9; 11,93</t>
+          <t>6,14; 12,09</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,36; 10,71</t>
+          <t>5,86; 10,7</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>10,55%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>8,38%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6,05%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9,31%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>7,32%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>6,81%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>6,76%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7,84%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>10,55%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>8,38%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6,05%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,97%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,36; 11,56</t>
+          <t>7,23; 15,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,67; 11,5</t>
+          <t>4,9; 12,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,91; 10,76</t>
+          <t>3,26; 9,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,91; 11,5</t>
+          <t>6,01; 13,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,02; 14,89</t>
+          <t>4,54; 12,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,04; 12,68</t>
+          <t>4,03; 11,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,22; 10,09</t>
+          <t>4,03; 10,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,27; 14,6</t>
+          <t>5,94; 12,93</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,55; 12,03</t>
+          <t>6,37; 11,84</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,37; 10,86</t>
+          <t>5,26; 10,45</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,24; 8,78</t>
+          <t>4,37; 9,1</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,43; 11,42</t>
+          <t>6,48; 11,79</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>7,97%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>9,17%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>6,62%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>7,85%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>6,56%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>10,17%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>8,52%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>5,97%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>7,97%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>9,17%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>6,62%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,96; 8,52</t>
+          <t>6,3; 9,94</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,18; 12,65</t>
+          <t>7,17; 11,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,62; 10,62</t>
+          <t>5,07; 8,45</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,47; 7,62</t>
+          <t>6,14; 9,92</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,19; 10,1</t>
+          <t>4,96; 8,53</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,1; 11,39</t>
+          <t>7,93; 12,53</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,02; 8,55</t>
+          <t>6,55; 10,48</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,46; 10,25</t>
+          <t>4,92; 8,22</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,97; 8,63</t>
+          <t>5,97; 8,62</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,18; 11,2</t>
+          <t>8,28; 11,27</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6,2; 8,78</t>
+          <t>6,37; 8,9</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,09; 8,67</t>
+          <t>6,02; 8,56</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>7577</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>8687</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>8994</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>5600</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>4904</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>8451</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>9516</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>5288</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>7577</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>8687</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>8994</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6294</t>
+          <t>5659</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11583</t>
+          <t>11259</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2169; 9787</t>
+          <t>4082; 12611</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4288; 14316</t>
+          <t>4716; 14677</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5218; 15462</t>
+          <t>4746; 14858</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2373; 10701</t>
+          <t>2813; 11448</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3844; 12397</t>
+          <t>2134; 10228</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4863; 15204</t>
+          <t>4346; 14400</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4891; 15264</t>
+          <t>5032; 15357</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2998; 11579</t>
+          <t>2357; 11959</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>7587; 19008</t>
+          <t>8079; 19078</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10925; 24200</t>
+          <t>11497; 24737</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12794; 27451</t>
+          <t>12281; 26295</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6736; 18232</t>
+          <t>6557; 18175</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>18</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>11379</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>12243</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>9653</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>17645</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>8364</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>14676</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>11666</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>10807</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>11379</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>12243</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>9653</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>19845</t>
+          <t>9552</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>30651</t>
+          <t>27198</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4522; 13470</t>
+          <t>6767; 17342</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9827; 21274</t>
+          <t>7009; 18658</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7315; 17774</t>
+          <t>5679; 15974</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6517; 17230</t>
+          <t>11101; 27090</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6718; 17919</t>
+          <t>4616; 13737</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7781; 18601</t>
+          <t>9368; 21134</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5675; 16574</t>
+          <t>7322; 17994</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12531; 30568</t>
+          <t>5746; 14777</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13722; 27132</t>
+          <t>14357; 28406</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>19646; 35616</t>
+          <t>19324; 35110</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15303; 30931</t>
+          <t>15121; 29042</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>21472; 44650</t>
+          <t>19450; 38671</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>6631</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>15479</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>9564</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>15894</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>7588</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>15421</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>12304</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>10232</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>6631</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>15479</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>9564</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18870</t>
+          <t>10092</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>29102</t>
+          <t>25986</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4008; 13325</t>
+          <t>3272; 11295</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10233; 22379</t>
+          <t>10069; 22098</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7619; 18284</t>
+          <t>5321; 16334</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5174; 17216</t>
+          <t>10274; 23816</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3310; 11699</t>
+          <t>4190; 12863</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9595; 21910</t>
+          <t>10177; 21586</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5024; 15741</t>
+          <t>7701; 18400</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>11773; 28436</t>
+          <t>5824; 16027</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>9057; 21306</t>
+          <t>9387; 21213</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>23097; 40184</t>
+          <t>23238; 40748</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>14722; 29753</t>
+          <t>15316; 30151</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>20045; 40057</t>
+          <t>18957; 34636</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>21</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>16564</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>12978</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>9535</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>15775</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>12105</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>9942</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>11237</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>13110</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>16564</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>12978</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>9535</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>17078</t>
+          <t>14334</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>30188</t>
+          <t>30109</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7210; 19111</t>
+          <t>11340; 23836</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5353; 16791</t>
+          <t>7595; 19340</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6502; 17873</t>
+          <t>5132; 15664</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8209; 19237</t>
+          <t>10177; 22858</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11023; 23374</t>
+          <t>7506; 19852</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7806; 19643</t>
+          <t>5879; 16063</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5078; 15892</t>
+          <t>6699; 18055</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>11356; 26464</t>
+          <t>9893; 21524</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>21113; 38764</t>
+          <t>20539; 38158</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>16147; 32677</t>
+          <t>15832; 31442</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>13710; 28425</t>
+          <t>14154; 29453</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>22392; 39790</t>
+          <t>21773; 39576</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>68</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>62</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>42151</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>49386</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>37745</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>54913</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>32961</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>48489</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>44723</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>39438</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>42151</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>49386</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>37745</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>62086</t>
+          <t>39637</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>101524</t>
+          <t>94550</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>24919; 42812</t>
+          <t>33274; 52542</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>39011; 60340</t>
+          <t>38616; 62296</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>34721; 55716</t>
+          <t>28893; 48170</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>29505; 50292</t>
+          <t>42903; 69325</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>32699; 53374</t>
+          <t>24916; 42840</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>38238; 61357</t>
+          <t>37802; 59783</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>28628; 48785</t>
+          <t>34354; 55005</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>49117; 77960</t>
+          <t>30673; 51187</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>61541; 88920</t>
+          <t>61548; 88815</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>83051; 113810</t>
+          <t>84091; 114490</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>67923; 96114</t>
+          <t>69808; 97438</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>86545; 123106</t>
+          <t>79571; 113243</t>
         </is>
       </c>
     </row>
